--- a/AAII_Financials/Quarterly/ZONE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZONE_QTR_FIN.xlsx
@@ -1182,7 +1182,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12700</v>
+        <v>19500</v>
       </c>
       <c r="E17" s="3">
         <v>21800</v>
@@ -1238,7 +1238,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-12200</v>
+        <v>-19000</v>
       </c>
       <c r="E18" s="3">
         <v>-20700</v>
@@ -1316,7 +1316,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>18700</v>
+        <v>18400</v>
       </c>
       <c r="E20" s="3">
         <v>83700</v>
@@ -1372,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-30800</v>
+        <v>-37300</v>
       </c>
       <c r="E21" s="3">
         <v>-104400</v>
@@ -1484,7 +1484,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-30800</v>
+        <v>-37300</v>
       </c>
       <c r="E23" s="3">
         <v>-104400</v>
@@ -1652,7 +1652,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-30800</v>
+        <v>-37300</v>
       </c>
       <c r="E26" s="3">
         <v>-104400</v>
@@ -1708,7 +1708,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-30800</v>
+        <v>-37300</v>
       </c>
       <c r="E27" s="3">
         <v>-104400</v>
@@ -1988,7 +1988,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-18700</v>
+        <v>-18400</v>
       </c>
       <c r="E32" s="3">
         <v>-83700</v>
@@ -2044,7 +2044,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-30800</v>
+        <v>-37300</v>
       </c>
       <c r="E33" s="3">
         <v>-104400</v>
@@ -2156,7 +2156,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-30800</v>
+        <v>-37300</v>
       </c>
       <c r="E35" s="3">
         <v>-104400</v>
@@ -2933,7 +2933,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>49200</v>
+        <v>42800</v>
       </c>
       <c r="E52" s="3">
         <v>86300</v>
@@ -3045,7 +3045,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>73900</v>
+        <v>67400</v>
       </c>
       <c r="E54" s="3">
         <v>101100</v>
@@ -3951,7 +3951,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-162600</v>
+        <v>-169000</v>
       </c>
       <c r="E72" s="3">
         <v>-131800</v>
@@ -4175,7 +4175,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>66800</v>
+        <v>60300</v>
       </c>
       <c r="E76" s="3">
         <v>93800</v>
@@ -4348,7 +4348,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-30800</v>
+        <v>-37300</v>
       </c>
       <c r="E81" s="3">
         <v>-104400</v>
